--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="131">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>RecordTarget.typeId.nullFlavor</t>
@@ -1266,7 +1270,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1274,10 +1278,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1375,17 +1379,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1403,11 +1407,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1458,7 +1462,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1478,17 +1482,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1506,11 +1510,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1561,7 +1565,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1581,17 +1585,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1609,11 +1613,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1622,7 +1626,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1664,7 +1668,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1684,17 +1688,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1712,11 +1716,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1767,7 +1771,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1787,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1817,7 +1821,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1868,7 +1872,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1888,10 +1892,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1925,7 +1929,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -1947,7 +1951,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1965,7 +1969,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -1985,10 +1989,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2022,7 +2026,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2044,7 +2048,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2062,7 +2066,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2082,10 +2086,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2108,7 +2112,7 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -2161,7 +2165,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="132">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -415,6 +415,9 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/PatientRole {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-patient-role}
 </t>
+  </si>
+  <si>
+    <t>Description du patient/usager.</t>
   </si>
 </sst>
 </file>
@@ -2114,7 +2117,9 @@
       <c r="K14" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" t="s" s="2">
+        <v>131</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Patient/Usager concerné par le document.</t>
+    <t>L'élément de l'en-tête du CDA recordTarget permet de représenter le patient/usager concerné par le document.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-record-target.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
